--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_topology_registry.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_topology_registry.xlsx
@@ -451,7 +451,7 @@
     <col width="39" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>d5-topology-evidence-20260726</t>
+          <t>d5-topology-evidence-20260727-inventory-reverified</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="P2" t="b">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
